--- a/詳細設計/02_詳細設計書_Checklist.xlsx
+++ b/詳細設計/02_詳細設計書_Checklist.xlsx
@@ -1,33 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="00_表紙" sheetId="1" ns1:id="Rcfea96a70a62426c"/>
-    <sheet name="01_改訂履歴" sheetId="2" ns1:id="R7bb9fa589d5d48fe"/>
-    <sheet name="02_共通" sheetId="3" ns1:id="Rd3ffef0dfd324740"/>
-    <sheet name="03_画面" sheetId="4" ns1:id="R36831fb54cab4ca1"/>
-    <sheet name="04_API" sheetId="5" ns1:id="Rdc519c50ec1e448d"/>
-    <sheet name="05_DB_SQL" sheetId="6" ns1:id="R288d72a05a5f4334"/>
-    <sheet name="06_非機能_安全" sheetId="7" ns1:id="R1c836c42ba9e498a"/>
-    <sheet name="07_Review記録" sheetId="8" ns1:id="R100d0fb7a5d44c33"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'00_表紙'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'01_改訂履歴'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'02_共通'!$A$1:$I$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'02_共通'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'03_画面'!$A$1:$I$25</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'03_画面'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'04_API'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'04_API'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'05_DB_SQL'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'05_DB_SQL'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'06_非機能_安全'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'06_非機能_安全'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'07_Review記録'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'07_Review記録'!$1:$7</definedName>
-  </definedNames>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R40e71f443cd04d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R62f1606a9f5545c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通" sheetId="3" r:id="R7967175aaaed483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面" sheetId="4" r:id="R6292c2e761b74a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API" sheetId="5" r:id="R096ad1cc96a844b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_DB_SQL" sheetId="6" r:id="Rf665cd36ab5346f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_非機能_安全" sheetId="7" r:id="Rad538525c7c74bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Review記録" sheetId="8" r:id="R9c01d92a390f4b92"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1060,7 +1044,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>Ver.1.0</x:v>
@@ -1077,8 +1061,8 @@
       <x:c r="D16" s="11" t="str">
         <x:v>作成日</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="n">
-        <x:v>46294</x:v>
+      <x:c r="E16" s="16" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
         <x:v>46240</x:v>
@@ -1457,7 +1441,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -1633,14 +1617,30 @@
       <x:c r="I11" s="65"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
+      <x:c r="A12" s="60" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B12" s="60" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="C12" s="66" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="D12" s="60" t="str">
+        <x:v>上流規則の具体的展開とFile／Sheet／ID／Baseline追跡をCheckへ反映。</x:v>
+      </x:c>
+      <x:c r="E12" s="60" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F12" s="60" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G12" s="60" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H12" s="60" t="str">
+        <x:v>修正済／Review待ち</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="2"/>
@@ -1929,7 +1929,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -2037,7 +2037,7 @@
       </x:c>
       <x:c r="C9" s="57"/>
       <x:c r="D9" s="57" t="str">
-        <x:v>基本設計の正本・Sheet・設計IDと参照版数が特定でき、未承認変更は承認済と区別されている。</x:v>
+        <x:v>対象機能に適用する基本設計の値・条件・業務規則・異常後状態を本書に具体的に展開し、根拠を基本設計File／Sheet／設計ID又はCell位置・Baselineで特定できる。参照先だけで処理内容を省略しない。</x:v>
       </x:c>
       <x:c r="E9" s="57" t="str">
         <x:v>未確認</x:v>
@@ -3189,7 +3189,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -4337,7 +4337,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -5497,7 +5497,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -6657,7 +6657,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -7827,7 +7827,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.4　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
